--- a/src/data/calibration_data_red.xlsx
+++ b/src/data/calibration_data_red.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F5A52429-250B-4FCB-B1CF-257C5FAB594C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB616FE-3B9E-4A12-B2BC-2DCF122AAB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62E85406-350A-40CB-A25D-865E512FD12D}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_red" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -895,10 +914,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC7DA88-F663-4D66-B4B5-64F1D8C47123}">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -909,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>50</v>
       </c>
@@ -931,23 +950,35 @@
         <f t="shared" si="0"/>
         <v>3.7936267071320183E-3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:K2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="1"/>
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="M2" t="s">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <f>AVERAGE(E2:E91)</f>
         <v>1.9313117509990426E-2</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:L2" si="1">AVERAGE(F2:F91)</f>
+      <c r="O2">
+        <f>AVERAGE(F2:F91)</f>
         <v>2.5718497818805483E-3</v>
       </c>
-      <c r="L2">
-        <f t="shared" si="1"/>
+      <c r="P2">
+        <f>AVERAGE(G2:G91)</f>
         <v>4.1514661760515392E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>51</v>
       </c>
@@ -969,23 +1000,35 @@
         <f t="shared" ref="G3:G65" si="4">C3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>3.5945363048166786E-3</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.72857142857142854</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.12857142857142856</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M3" t="s">
         <v>4</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <f>_xlfn.STDEV.P(E2:E91)</f>
         <v>7.3427832082027095E-4</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:L3" si="5">_xlfn.STDEV.P(F2:F91)</f>
+      <c r="O3">
+        <f>_xlfn.STDEV.P(F2:F91)</f>
         <v>3.5374882040563891E-4</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="5"/>
+      <c r="P3">
+        <f>_xlfn.STDEV.P(G2:G91)</f>
         <v>3.3072673956052577E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>50</v>
       </c>
@@ -1007,8 +1050,20 @@
         <f t="shared" si="4"/>
         <v>3.4390523500191059E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="5"/>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="7"/>
+        <v>0.13846153846153847</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>51</v>
       </c>
@@ -1030,8 +1085,35 @@
         <f t="shared" si="4"/>
         <v>3.9696860339227718E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="6"/>
+        <v>0.10144927536231885</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="7"/>
+        <v>0.15942028985507245</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>AVERAGE(I2:I91)</f>
+        <v>0.7418242883883116</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:P5" si="8">AVERAGE(J2:J91)</f>
+        <v>9.8789985537513086E-2</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="8"/>
+        <v>0.15938572607417509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>46</v>
       </c>
@@ -1053,8 +1135,35 @@
         <f t="shared" si="4"/>
         <v>4.0504050405040506E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="5"/>
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="6"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.STDEV.P(I2:I91)</f>
+        <v>1.9852984860585652E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" ref="O6:P6" si="9">_xlfn.STDEV.P(J2:J91)</f>
+        <v>1.3327675736043019E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="9"/>
+        <v>1.1013702594048831E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>51</v>
       </c>
@@ -1076,8 +1185,20 @@
         <f t="shared" si="4"/>
         <v>3.9696860339227718E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="5"/>
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>0.10144927536231885</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>0.15942028985507245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>49</v>
       </c>
@@ -1099,8 +1220,20 @@
         <f t="shared" si="4"/>
         <v>4.3002345582486314E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="5"/>
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>51</v>
       </c>
@@ -1122,8 +1255,20 @@
         <f t="shared" si="4"/>
         <v>4.271982912068352E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.71830985915492962</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>0.11267605633802817</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.16901408450704225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>50</v>
       </c>
@@ -1145,8 +1290,20 @@
         <f t="shared" si="4"/>
         <v>4.7272727272727275E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>0.125</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="7"/>
+        <v>0.18055555555555555</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>49</v>
       </c>
@@ -1168,8 +1325,20 @@
         <f t="shared" si="4"/>
         <v>4.3002345582486314E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>50</v>
       </c>
@@ -1191,8 +1360,20 @@
         <f t="shared" si="4"/>
         <v>4.1400075272864136E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.74626865671641796</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>8.9552238805970144E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>49</v>
       </c>
@@ -1214,8 +1395,20 @@
         <f t="shared" si="4"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="7"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>50</v>
       </c>
@@ -1237,8 +1430,20 @@
         <f t="shared" si="4"/>
         <v>3.7936267071320183E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="7"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>49</v>
       </c>
@@ -1260,8 +1465,20 @@
         <f t="shared" si="4"/>
         <v>5.2277819268110532E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>0.125</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>0.19444444444444445</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>49</v>
       </c>
@@ -1283,8 +1500,20 @@
         <f t="shared" si="4"/>
         <v>4.2784908595877094E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>48</v>
       </c>
@@ -1306,8 +1535,20 @@
         <f t="shared" si="4"/>
         <v>4.1169205434335113E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>7.9365079365079361E-2</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>51</v>
       </c>
@@ -1329,8 +1570,20 @@
         <f t="shared" si="4"/>
         <v>2.9618659755646058E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.7846153846153846</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="7"/>
+        <v>0.12307692307692308</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>49</v>
       </c>
@@ -1352,8 +1605,20 @@
         <f t="shared" si="4"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="7"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>50</v>
       </c>
@@ -1375,8 +1640,20 @@
         <f t="shared" si="4"/>
         <v>4.1400075272864136E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.74626865671641796</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>8.9552238805970144E-2</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>48</v>
       </c>
@@ -1398,8 +1675,20 @@
         <f t="shared" si="4"/>
         <v>4.1169205434335113E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>7.9365079365079361E-2</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>49</v>
       </c>
@@ -1421,8 +1710,20 @@
         <f t="shared" si="4"/>
         <v>3.95882818685669E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.765625</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>7.8125E-2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>53</v>
       </c>
@@ -1444,8 +1745,20 @@
         <f t="shared" si="4"/>
         <v>4.7543581616481777E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.67088607594936711</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>0.13924050632911392</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="7"/>
+        <v>0.189873417721519</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>48</v>
       </c>
@@ -1467,8 +1780,20 @@
         <f t="shared" si="4"/>
         <v>4.1169205434335113E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>7.9365079365079361E-2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>49</v>
       </c>
@@ -1490,8 +1815,20 @@
         <f t="shared" si="4"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="7"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>50</v>
       </c>
@@ -1513,8 +1850,20 @@
         <f t="shared" si="4"/>
         <v>4.1400075272864136E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>0.74626865671641796</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>8.9552238805970144E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>50</v>
       </c>
@@ -1536,8 +1885,20 @@
         <f t="shared" si="4"/>
         <v>4.0968342644320298E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.72463768115942029</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>0.11594202898550725</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.15942028985507245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>51</v>
       </c>
@@ -1559,8 +1920,20 @@
         <f t="shared" si="4"/>
         <v>3.9483129935391241E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="5"/>
+        <v>0.72857142857142854</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="7"/>
+        <v>0.15714285714285714</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>49</v>
       </c>
@@ -1582,8 +1955,20 @@
         <f t="shared" si="4"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="5"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="6"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>49</v>
       </c>
@@ -1605,8 +1990,20 @@
         <f t="shared" si="4"/>
         <v>4.6260601387818042E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0.72058823529411764</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="7"/>
+        <v>0.17647058823529413</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>48</v>
       </c>
@@ -1628,8 +2025,20 @@
         <f t="shared" si="4"/>
         <v>3.7344398340248964E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>8.0645161290322578E-2</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="7"/>
+        <v>0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>47</v>
       </c>
@@ -1651,8 +2060,20 @@
         <f t="shared" si="4"/>
         <v>4.2408821034775231E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="5"/>
+        <v>0.734375</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>0.109375</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>49</v>
       </c>
@@ -1674,8 +2095,20 @@
         <f t="shared" si="4"/>
         <v>3.9215686274509803E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="5"/>
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.10606060606060606</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>47</v>
       </c>
@@ -1697,8 +2130,20 @@
         <f t="shared" si="4"/>
         <v>4.6491969568892644E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="5"/>
+        <v>0.734375</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="6"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="7"/>
+        <v>0.171875</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>47</v>
       </c>
@@ -1720,8 +2165,20 @@
         <f t="shared" si="4"/>
         <v>3.869303525365434E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="5"/>
+        <v>0.75806451612903225</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="6"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="7"/>
+        <v>0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>47</v>
       </c>
@@ -1743,8 +2200,20 @@
         <f t="shared" si="4"/>
         <v>4.2643923240938165E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>46</v>
       </c>
@@ -1766,8 +2235,20 @@
         <f t="shared" si="4"/>
         <v>4.0668775417984637E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="5"/>
+        <v>0.77966101694915257</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="7"/>
+        <v>0.15254237288135594</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>48</v>
       </c>
@@ -1789,8 +2270,20 @@
         <f t="shared" si="4"/>
         <v>4.4194455604660505E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="5"/>
+        <v>0.71641791044776115</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>0.11940298507462686</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>46</v>
       </c>
@@ -1812,8 +2305,20 @@
         <f t="shared" si="4"/>
         <v>4.0504050405040506E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>47</v>
       </c>
@@ -1835,8 +2340,20 @@
         <f t="shared" si="4"/>
         <v>4.6237915090374107E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>0.72307692307692306</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="7"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>48</v>
       </c>
@@ -1858,8 +2375,20 @@
         <f t="shared" si="4"/>
         <v>3.6749693752552064E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="5"/>
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>0.12307692307692308</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>0.13846153846153847</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>48</v>
       </c>
@@ -1881,8 +2410,20 @@
         <f t="shared" si="4"/>
         <v>4.7770700636942673E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="5"/>
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="7"/>
+        <v>0.17647058823529413</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>47</v>
       </c>
@@ -1904,8 +2445,20 @@
         <f t="shared" si="4"/>
         <v>4.6237915090374107E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="5"/>
+        <v>0.72307692307692306</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="7"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>47</v>
       </c>
@@ -1927,8 +2480,20 @@
         <f t="shared" si="4"/>
         <v>4.2643923240938165E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="5"/>
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>47</v>
       </c>
@@ -1950,8 +2515,20 @@
         <f t="shared" si="4"/>
         <v>4.2643923240938165E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="5"/>
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>48</v>
       </c>
@@ -1973,8 +2550,20 @@
         <f t="shared" si="4"/>
         <v>3.6976170912078883E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>0.109375</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="7"/>
+        <v>0.140625</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>49</v>
       </c>
@@ -1996,8 +2585,20 @@
         <f t="shared" si="4"/>
         <v>3.9215686274509803E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="5"/>
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>0.10606060606060606</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="7"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2019,8 +2620,20 @@
         <f t="shared" si="4"/>
         <v>4.6237915090374107E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="5"/>
+        <v>0.72307692307692306</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="7"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2042,8 +2655,20 @@
         <f t="shared" si="4"/>
         <v>3.8876889848812094E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="5"/>
+        <v>0.77049180327868849</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>8.1967213114754092E-2</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="7"/>
+        <v>0.14754098360655737</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>47</v>
       </c>
@@ -2065,8 +2690,20 @@
         <f t="shared" si="4"/>
         <v>3.9028620988725065E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>46</v>
       </c>
@@ -2088,8 +2725,20 @@
         <f t="shared" si="4"/>
         <v>4.4622936189201252E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="5"/>
+        <v>0.75409836065573765</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>8.1967213114754092E-2</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="7"/>
+        <v>0.16393442622950818</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>48</v>
       </c>
@@ -2111,8 +2760,20 @@
         <f t="shared" si="4"/>
         <v>3.7174721189591076E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="5"/>
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>45</v>
       </c>
@@ -2134,8 +2795,20 @@
         <f t="shared" si="4"/>
         <v>4.2233693101830123E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="5"/>
+        <v>0.76271186440677963</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>8.4745762711864403E-2</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="7"/>
+        <v>0.15254237288135594</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>47</v>
       </c>
@@ -2157,8 +2830,20 @@
         <f t="shared" si="4"/>
         <v>3.869303525365434E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="5"/>
+        <v>0.75806451612903225</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="7"/>
+        <v>0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>48</v>
       </c>
@@ -2180,8 +2865,20 @@
         <f t="shared" si="4"/>
         <v>4.4194455604660505E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="5"/>
+        <v>0.71641791044776115</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>0.11940298507462686</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="7"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>47</v>
       </c>
@@ -2203,8 +2900,20 @@
         <f t="shared" si="4"/>
         <v>4.6491969568892644E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="5"/>
+        <v>0.734375</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="7"/>
+        <v>0.171875</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>47</v>
       </c>
@@ -2226,8 +2935,20 @@
         <f t="shared" si="4"/>
         <v>4.6237915090374107E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="5"/>
+        <v>0.72307692307692306</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="7"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>49</v>
       </c>
@@ -2249,8 +2970,20 @@
         <f t="shared" si="4"/>
         <v>3.8986354775828458E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="5"/>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>0.11940298507462686</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="7"/>
+        <v>0.14925373134328357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>48</v>
       </c>
@@ -2272,8 +3005,20 @@
         <f t="shared" si="4"/>
         <v>3.7174721189591076E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="5"/>
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>46</v>
       </c>
@@ -2295,8 +3040,20 @@
         <f t="shared" si="4"/>
         <v>4.4404973357015983E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="5"/>
+        <v>0.74193548387096775</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="7"/>
+        <v>0.16129032258064516</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>47</v>
       </c>
@@ -2318,8 +3075,20 @@
         <f t="shared" si="4"/>
         <v>4.2643923240938165E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="5"/>
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="7"/>
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>50</v>
       </c>
@@ -2341,8 +3110,20 @@
         <f t="shared" si="4"/>
         <v>4.4313146233382573E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="5"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="7"/>
+        <v>0.17142857142857143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>49</v>
       </c>
@@ -2364,8 +3145,20 @@
         <f t="shared" si="4"/>
         <v>4.3002345582486314E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="5"/>
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>51</v>
       </c>
@@ -2387,8 +3180,20 @@
         <f t="shared" si="4"/>
         <v>4.2949176807444527E-3</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="5"/>
+        <v>0.72857142857142854</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="7"/>
+        <v>0.17142857142857143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>50</v>
       </c>
@@ -2410,8 +3215,20 @@
         <f t="shared" si="4"/>
         <v>4.1198501872659176E-3</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="5"/>
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="7"/>
+        <v>0.16176470588235295</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>51</v>
       </c>
@@ -2422,19 +3239,31 @@
         <v>12</v>
       </c>
       <c r="E66">
-        <f t="shared" ref="E66:E90" si="6">A66/($A66^2 + $B66^2 + $C66^2)</f>
+        <f t="shared" ref="E66:E90" si="10">A66/($A66^2 + $B66^2 + $C66^2)</f>
         <v>1.8155927376290494E-2</v>
       </c>
       <c r="F66">
-        <f t="shared" ref="F66:F91" si="7">B66/($A66^2 + $B66^2 + $C66^2)</f>
+        <f t="shared" ref="F66:F91" si="11">B66/($A66^2 + $B66^2 + $C66^2)</f>
         <v>2.847988608045568E-3</v>
       </c>
       <c r="G66">
-        <f t="shared" ref="G66:G91" si="8">C66/($A66^2 + $B66^2 + $C66^2)</f>
+        <f t="shared" ref="G66:G91" si="12">C66/($A66^2 + $B66^2 + $C66^2)</f>
         <v>4.271982912068352E-3</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="5"/>
+        <v>0.71830985915492962</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>0.11267605633802817</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="7"/>
+        <v>0.16901408450704225</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>48</v>
       </c>
@@ -2445,19 +3274,31 @@
         <v>11</v>
       </c>
       <c r="E67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.950426655830963E-2</v>
       </c>
       <c r="F67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4380333197887038E-3</v>
       </c>
       <c r="G67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.469727752945957E-3</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I91" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J91" si="14">B67/($A67+$B67+$C67)</f>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K91" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>49</v>
       </c>
@@ -2468,19 +3309,31 @@
         <v>10</v>
       </c>
       <c r="E68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9314150571541192E-2</v>
       </c>
       <c r="F68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.3649980291683089E-3</v>
       </c>
       <c r="G68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="13"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="14"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="15"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>47</v>
       </c>
@@ -2491,19 +3344,31 @@
         <v>10</v>
       </c>
       <c r="E69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.0137103684661525E-2</v>
       </c>
       <c r="F69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1422450728363325E-3</v>
       </c>
       <c r="G69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2844901456726651E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="13"/>
+        <v>0.75806451612903225</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="14"/>
+        <v>8.0645161290322578E-2</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="15"/>
+        <v>0.16129032258064516</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>48</v>
       </c>
@@ -2514,19 +3379,31 @@
         <v>11</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.950426655830963E-2</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4380333197887038E-3</v>
       </c>
       <c r="G70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.469727752945957E-3</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="13"/>
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="14"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>49</v>
       </c>
@@ -2537,19 +3414,31 @@
         <v>11</v>
       </c>
       <c r="E71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9058732010890703E-2</v>
       </c>
       <c r="F71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.7226760015558148E-3</v>
       </c>
       <c r="G71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2784908595877094E-3</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="13"/>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="14"/>
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="15"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>51</v>
       </c>
@@ -2560,19 +3449,31 @@
         <v>11</v>
       </c>
       <c r="E72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8404907975460124E-2</v>
       </c>
       <c r="F72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.5261638397690365E-3</v>
       </c>
       <c r="G72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.9696860339227718E-3</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="13"/>
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="14"/>
+        <v>0.10144927536231885</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="15"/>
+        <v>0.15942028985507245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>47</v>
       </c>
@@ -2583,19 +3484,31 @@
         <v>10</v>
       </c>
       <c r="E73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9932145886344361E-2</v>
       </c>
       <c r="F73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.9686174724342664E-3</v>
       </c>
       <c r="G73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2408821034775231E-3</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="13"/>
+        <v>0.734375</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="14"/>
+        <v>0.109375</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="15"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>49</v>
       </c>
@@ -2606,19 +3519,31 @@
         <v>10</v>
       </c>
       <c r="E74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9314150571541192E-2</v>
       </c>
       <c r="F74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.3649980291683089E-3</v>
       </c>
       <c r="G74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="13"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="14"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="15"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>50</v>
       </c>
@@ -2629,19 +3554,31 @@
         <v>10</v>
       </c>
       <c r="E75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8968133535660091E-2</v>
       </c>
       <c r="F75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.276176024279211E-3</v>
       </c>
       <c r="G75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7936267071320183E-3</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="13"/>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="14"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="15"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>49</v>
       </c>
@@ -2652,19 +3589,31 @@
         <v>11</v>
       </c>
       <c r="E76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9058732010890703E-2</v>
       </c>
       <c r="F76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.7226760015558148E-3</v>
       </c>
       <c r="G76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2784908595877094E-3</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <f t="shared" si="13"/>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="14"/>
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="15"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>50</v>
       </c>
@@ -2675,19 +3624,31 @@
         <v>11</v>
       </c>
       <c r="E77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8726591760299626E-2</v>
       </c>
       <c r="F77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6217228464419477E-3</v>
       </c>
       <c r="G77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.1198501872659176E-3</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <f t="shared" si="13"/>
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="14"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="15"/>
+        <v>0.16176470588235295</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>51</v>
       </c>
@@ -2698,19 +3659,31 @@
         <v>13</v>
       </c>
       <c r="E78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8091521816246896E-2</v>
       </c>
       <c r="F78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4831500532103584E-3</v>
       </c>
       <c r="G78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.6115643845335225E-3</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <f t="shared" si="13"/>
+        <v>0.71830985915492962</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="14"/>
+        <v>9.8591549295774641E-2</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="15"/>
+        <v>0.18309859154929578</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>50</v>
       </c>
@@ -2721,19 +3694,31 @@
         <v>10</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8875047187617969E-2</v>
       </c>
       <c r="F79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6425066062665155E-3</v>
       </c>
       <c r="G79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.7750094375235939E-3</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <f t="shared" si="13"/>
+        <v>0.74626865671641796</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="14"/>
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="15"/>
+        <v>0.14925373134328357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>50</v>
       </c>
@@ -2744,19 +3729,31 @@
         <v>11</v>
       </c>
       <c r="E80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8726591760299626E-2</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6217228464419477E-3</v>
       </c>
       <c r="G80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.1198501872659176E-3</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <f t="shared" si="13"/>
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="14"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="15"/>
+        <v>0.16176470588235295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>48</v>
       </c>
@@ -2767,19 +3764,31 @@
         <v>11</v>
       </c>
       <c r="E81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.950426655830963E-2</v>
       </c>
       <c r="F81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4380333197887038E-3</v>
       </c>
       <c r="G81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.469727752945957E-3</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <f t="shared" si="13"/>
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="14"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="15"/>
+        <v>0.16923076923076924</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>50</v>
       </c>
@@ -2790,19 +3799,31 @@
         <v>11</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8726591760299626E-2</v>
       </c>
       <c r="F82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6217228464419477E-3</v>
       </c>
       <c r="G82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.1198501872659176E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <f t="shared" si="13"/>
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="14"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="15"/>
+        <v>0.16176470588235295</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>48</v>
       </c>
@@ -2813,19 +3834,31 @@
         <v>10</v>
       </c>
       <c r="E83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9672131147540985E-2</v>
       </c>
       <c r="F83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4590163934426232E-3</v>
       </c>
       <c r="G83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.0983606557377051E-3</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="14"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="15"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>49</v>
       </c>
@@ -2836,19 +3869,31 @@
         <v>11</v>
       </c>
       <c r="E84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9058732010890703E-2</v>
       </c>
       <c r="F84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.7226760015558148E-3</v>
       </c>
       <c r="G84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2784908595877094E-3</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <f t="shared" si="13"/>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="14"/>
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="15"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>50</v>
       </c>
@@ -2859,19 +3904,31 @@
         <v>11</v>
       </c>
       <c r="E85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.86219739292365E-2</v>
       </c>
       <c r="F85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.9795158286778397E-3</v>
       </c>
       <c r="G85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.0968342644320298E-3</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <f t="shared" si="13"/>
+        <v>0.72463768115942029</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="14"/>
+        <v>0.11594202898550725</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="15"/>
+        <v>0.15942028985507245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>47</v>
       </c>
@@ -2882,19 +3939,31 @@
         <v>10</v>
       </c>
       <c r="E86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.0137103684661525E-2</v>
       </c>
       <c r="F86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1422450728363325E-3</v>
       </c>
       <c r="G86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2844901456726651E-3</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <f t="shared" si="13"/>
+        <v>0.75806451612903225</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="14"/>
+        <v>8.0645161290322578E-2</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="15"/>
+        <v>0.16129032258064516</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>50</v>
       </c>
@@ -2905,19 +3974,31 @@
         <v>11</v>
       </c>
       <c r="E87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8726591760299626E-2</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.6217228464419477E-3</v>
       </c>
       <c r="G87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.1198501872659176E-3</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <f t="shared" si="13"/>
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="14"/>
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>0.16176470588235295</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>49</v>
       </c>
@@ -2928,19 +4009,31 @@
         <v>10</v>
       </c>
       <c r="E88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9314150571541192E-2</v>
       </c>
       <c r="F88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.3649980291683089E-3</v>
       </c>
       <c r="G88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.941663381947182E-3</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <f t="shared" si="13"/>
+        <v>0.75384615384615383</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="14"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="15"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>51</v>
       </c>
@@ -2951,19 +4044,31 @@
         <v>11</v>
       </c>
       <c r="E89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8305814788226848E-2</v>
       </c>
       <c r="F89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.871500358937545E-3</v>
       </c>
       <c r="G89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.9483129935391241E-3</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <f t="shared" si="13"/>
+        <v>0.72857142857142854</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="14"/>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="15"/>
+        <v>0.15714285714285714</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>48</v>
       </c>
@@ -2974,19 +4079,31 @@
         <v>10</v>
       </c>
       <c r="E90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.9672131147540985E-2</v>
       </c>
       <c r="F90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4590163934426232E-3</v>
       </c>
       <c r="G90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.0983606557377051E-3</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I90">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="14"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="15"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>48</v>
       </c>
@@ -3001,12 +4118,24 @@
         <v>1.9672131147540985E-2</v>
       </c>
       <c r="F91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.4590163934426232E-3</v>
       </c>
       <c r="G91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.0983606557377051E-3</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="14"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="15"/>
+        <v>0.15625</v>
       </c>
     </row>
   </sheetData>
